--- a/ResourcesTH/dsrProfileData.xlsx
+++ b/ResourcesTH/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="123">
   <si>
     <t>DT Code*</t>
   </si>
@@ -328,6 +328,66 @@
   </si>
   <si>
     <t>EMPE5F892</t>
+  </si>
+  <si>
+    <t>AUTO_00AE</t>
+  </si>
+  <si>
+    <t>AUTO_0798F</t>
+  </si>
+  <si>
+    <t>Father_00A9</t>
+  </si>
+  <si>
+    <t>03656011100</t>
+  </si>
+  <si>
+    <t>EMPA088EE</t>
+  </si>
+  <si>
+    <t>AUTO_0E63</t>
+  </si>
+  <si>
+    <t>AUTO_0DA08</t>
+  </si>
+  <si>
+    <t>Father_81DF</t>
+  </si>
+  <si>
+    <t>03661588600</t>
+  </si>
+  <si>
+    <t>EMPDEACF5</t>
+  </si>
+  <si>
+    <t>AUTO_3CB8</t>
+  </si>
+  <si>
+    <t>AUTO_5AD28</t>
+  </si>
+  <si>
+    <t>Father_168F</t>
+  </si>
+  <si>
+    <t>03040889600</t>
+  </si>
+  <si>
+    <t>EMPD561F8</t>
+  </si>
+  <si>
+    <t>AUTO_EC32</t>
+  </si>
+  <si>
+    <t>AUTO_CE13B</t>
+  </si>
+  <si>
+    <t>Father_CBE5</t>
+  </si>
+  <si>
+    <t>03046725000</t>
+  </si>
+  <si>
+    <t>EMP27DA67</t>
   </si>
 </sst>
 </file>
@@ -794,22 +854,22 @@
         <v>34</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>36</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>41</v>
@@ -898,22 +958,22 @@
         <v>34</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>36</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>41</v>
